--- a/Decks/Jhoira.xlsx
+++ b/Decks/Jhoira.xlsx
@@ -5,10 +5,10 @@
   <workbookPr codeName="EstaPastaDeTrabalho" defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Marcelo Scalvi\Dropbox\Jogos\Magic\Decks\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Marcelo Scalvi\Dropbox\Jogos\TheMagicCollection\Decks\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A234C544-92A2-40AE-A924-4361AA6EDF31}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BE2D9EF8-F6A7-44F0-91E2-B8CCECE6389C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{3A3EB0A0-3066-449C-BD01-AEAF92EDBA4C}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="306" uniqueCount="97">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="306" uniqueCount="98">
   <si>
     <t>Função</t>
   </si>
@@ -80,9 +80,6 @@
     <t>Command Tower</t>
   </si>
   <si>
-    <t>Ilha</t>
-  </si>
-  <si>
     <t>Valfenda</t>
   </si>
   <si>
@@ -92,9 +89,6 @@
     <t>Agna Qel'a</t>
   </si>
   <si>
-    <t>Montanha</t>
-  </si>
-  <si>
     <t>Bichão</t>
   </si>
   <si>
@@ -152,9 +146,6 @@
     <t>Aminatou's Augury</t>
   </si>
   <si>
-    <t>Dilatação da Mente</t>
-  </si>
-  <si>
     <t>Final</t>
   </si>
   <si>
@@ -182,9 +173,6 @@
     <t>Whelming Wave</t>
   </si>
   <si>
-    <t>Evacuação</t>
-  </si>
-  <si>
     <t>Chain Reaction</t>
   </si>
   <si>
@@ -314,9 +302,6 @@
     <t>Serum Visions</t>
   </si>
   <si>
-    <t>Antecipar</t>
-  </si>
-  <si>
     <t>Impulse</t>
   </si>
   <si>
@@ -327,6 +312,24 @@
   </si>
   <si>
     <t>Sleight of Hand</t>
+  </si>
+  <si>
+    <t>Improvisation Capstone</t>
+  </si>
+  <si>
+    <t>Mind's Dilation</t>
+  </si>
+  <si>
+    <t>Mountain</t>
+  </si>
+  <si>
+    <t>Island</t>
+  </si>
+  <si>
+    <t>Evacuation</t>
+  </si>
+  <si>
+    <t>Antecipate</t>
   </si>
 </sst>
 </file>
@@ -859,10 +862,10 @@
         <v>1</v>
       </c>
       <c r="C8" s="6" t="s">
+        <v>95</v>
+      </c>
+      <c r="D8" s="6" t="s">
         <v>14</v>
-      </c>
-      <c r="D8" s="6" t="s">
-        <v>15</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
@@ -874,10 +877,10 @@
         <v>1</v>
       </c>
       <c r="C9" s="6" t="s">
-        <v>14</v>
+        <v>95</v>
       </c>
       <c r="D9" s="6" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
@@ -889,10 +892,10 @@
         <v>1</v>
       </c>
       <c r="C10" s="6" t="s">
-        <v>14</v>
+        <v>95</v>
       </c>
       <c r="D10" s="6" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
@@ -904,10 +907,10 @@
         <v>0</v>
       </c>
       <c r="C11" s="6" t="s">
-        <v>14</v>
+        <v>95</v>
       </c>
       <c r="D11" s="6" t="s">
-        <v>14</v>
+        <v>95</v>
       </c>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.25">
@@ -919,10 +922,10 @@
         <v>0</v>
       </c>
       <c r="C12" s="6" t="s">
-        <v>14</v>
+        <v>95</v>
       </c>
       <c r="D12" s="6" t="s">
-        <v>14</v>
+        <v>95</v>
       </c>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.25">
@@ -934,10 +937,10 @@
         <v>0</v>
       </c>
       <c r="C13" s="6" t="s">
-        <v>14</v>
+        <v>95</v>
       </c>
       <c r="D13" s="6" t="s">
-        <v>14</v>
+        <v>95</v>
       </c>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.25">
@@ -949,10 +952,10 @@
         <v>0</v>
       </c>
       <c r="C14" s="6" t="s">
-        <v>14</v>
+        <v>95</v>
       </c>
       <c r="D14" s="6" t="s">
-        <v>14</v>
+        <v>95</v>
       </c>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.25">
@@ -964,10 +967,10 @@
         <v>0</v>
       </c>
       <c r="C15" s="6" t="s">
-        <v>14</v>
+        <v>95</v>
       </c>
       <c r="D15" s="6" t="s">
-        <v>14</v>
+        <v>95</v>
       </c>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.25">
@@ -979,10 +982,10 @@
         <v>0</v>
       </c>
       <c r="C16" s="6" t="s">
-        <v>14</v>
+        <v>95</v>
       </c>
       <c r="D16" s="6" t="s">
-        <v>14</v>
+        <v>95</v>
       </c>
     </row>
     <row r="17" spans="1:4" x14ac:dyDescent="0.25">
@@ -994,10 +997,10 @@
         <v>0</v>
       </c>
       <c r="C17" s="6" t="s">
-        <v>14</v>
+        <v>95</v>
       </c>
       <c r="D17" s="6" t="s">
-        <v>14</v>
+        <v>95</v>
       </c>
     </row>
     <row r="18" spans="1:4" x14ac:dyDescent="0.25">
@@ -1009,10 +1012,10 @@
         <v>0</v>
       </c>
       <c r="C18" s="6" t="s">
-        <v>14</v>
+        <v>95</v>
       </c>
       <c r="D18" s="6" t="s">
-        <v>14</v>
+        <v>95</v>
       </c>
     </row>
     <row r="19" spans="1:4" x14ac:dyDescent="0.25">
@@ -1024,10 +1027,10 @@
         <v>0</v>
       </c>
       <c r="C19" s="6" t="s">
-        <v>14</v>
+        <v>95</v>
       </c>
       <c r="D19" s="6" t="s">
-        <v>14</v>
+        <v>95</v>
       </c>
     </row>
     <row r="20" spans="1:4" x14ac:dyDescent="0.25">
@@ -1039,10 +1042,10 @@
         <v>0</v>
       </c>
       <c r="C20" s="6" t="s">
-        <v>14</v>
+        <v>95</v>
       </c>
       <c r="D20" s="6" t="s">
-        <v>14</v>
+        <v>95</v>
       </c>
     </row>
     <row r="21" spans="1:4" x14ac:dyDescent="0.25">
@@ -1054,10 +1057,10 @@
         <v>0</v>
       </c>
       <c r="C21" s="6" t="s">
-        <v>14</v>
+        <v>95</v>
       </c>
       <c r="D21" s="6" t="s">
-        <v>14</v>
+        <v>95</v>
       </c>
     </row>
     <row r="22" spans="1:4" x14ac:dyDescent="0.25">
@@ -1069,10 +1072,10 @@
         <v>0</v>
       </c>
       <c r="C22" s="6" t="s">
-        <v>14</v>
+        <v>95</v>
       </c>
       <c r="D22" s="6" t="s">
-        <v>14</v>
+        <v>95</v>
       </c>
     </row>
     <row r="23" spans="1:4" x14ac:dyDescent="0.25">
@@ -1084,10 +1087,10 @@
         <v>0</v>
       </c>
       <c r="C23" s="6" t="s">
-        <v>18</v>
+        <v>94</v>
       </c>
       <c r="D23" s="6" t="s">
-        <v>18</v>
+        <v>94</v>
       </c>
     </row>
     <row r="24" spans="1:4" x14ac:dyDescent="0.25">
@@ -1099,10 +1102,10 @@
         <v>0</v>
       </c>
       <c r="C24" s="6" t="s">
-        <v>18</v>
+        <v>94</v>
       </c>
       <c r="D24" s="6" t="s">
-        <v>18</v>
+        <v>94</v>
       </c>
     </row>
     <row r="25" spans="1:4" x14ac:dyDescent="0.25">
@@ -1114,10 +1117,10 @@
         <v>0</v>
       </c>
       <c r="C25" s="6" t="s">
-        <v>18</v>
+        <v>94</v>
       </c>
       <c r="D25" s="6" t="s">
-        <v>18</v>
+        <v>94</v>
       </c>
     </row>
     <row r="26" spans="1:4" x14ac:dyDescent="0.25">
@@ -1129,10 +1132,10 @@
         <v>0</v>
       </c>
       <c r="C26" s="6" t="s">
-        <v>18</v>
+        <v>94</v>
       </c>
       <c r="D26" s="6" t="s">
-        <v>18</v>
+        <v>94</v>
       </c>
     </row>
     <row r="27" spans="1:4" x14ac:dyDescent="0.25">
@@ -1144,10 +1147,10 @@
         <v>0</v>
       </c>
       <c r="C27" s="6" t="s">
-        <v>18</v>
+        <v>94</v>
       </c>
       <c r="D27" s="6" t="s">
-        <v>18</v>
+        <v>94</v>
       </c>
     </row>
     <row r="28" spans="1:4" x14ac:dyDescent="0.25">
@@ -1159,10 +1162,10 @@
         <v>0</v>
       </c>
       <c r="C28" s="6" t="s">
-        <v>18</v>
+        <v>94</v>
       </c>
       <c r="D28" s="6" t="s">
-        <v>18</v>
+        <v>94</v>
       </c>
     </row>
     <row r="29" spans="1:4" x14ac:dyDescent="0.25">
@@ -1174,10 +1177,10 @@
         <v>0</v>
       </c>
       <c r="C29" s="6" t="s">
-        <v>18</v>
+        <v>94</v>
       </c>
       <c r="D29" s="6" t="s">
-        <v>18</v>
+        <v>94</v>
       </c>
     </row>
     <row r="30" spans="1:4" x14ac:dyDescent="0.25">
@@ -1189,10 +1192,10 @@
         <v>0</v>
       </c>
       <c r="C30" s="6" t="s">
-        <v>18</v>
+        <v>94</v>
       </c>
       <c r="D30" s="6" t="s">
-        <v>18</v>
+        <v>94</v>
       </c>
     </row>
     <row r="31" spans="1:4" x14ac:dyDescent="0.25">
@@ -1204,10 +1207,10 @@
         <v>0</v>
       </c>
       <c r="C31" s="6" t="s">
-        <v>18</v>
+        <v>94</v>
       </c>
       <c r="D31" s="6" t="s">
-        <v>18</v>
+        <v>94</v>
       </c>
     </row>
     <row r="32" spans="1:4" x14ac:dyDescent="0.25">
@@ -1219,10 +1222,10 @@
         <v>0</v>
       </c>
       <c r="C32" s="6" t="s">
-        <v>18</v>
+        <v>94</v>
       </c>
       <c r="D32" s="6" t="s">
-        <v>18</v>
+        <v>94</v>
       </c>
     </row>
     <row r="33" spans="1:4" x14ac:dyDescent="0.25">
@@ -1234,10 +1237,10 @@
         <v>0</v>
       </c>
       <c r="C33" s="6" t="s">
-        <v>18</v>
+        <v>94</v>
       </c>
       <c r="D33" s="6" t="s">
-        <v>18</v>
+        <v>94</v>
       </c>
     </row>
     <row r="34" spans="1:4" x14ac:dyDescent="0.25">
@@ -1249,1015 +1252,1015 @@
         <v>0</v>
       </c>
       <c r="C34" s="6" t="s">
-        <v>18</v>
+        <v>94</v>
       </c>
       <c r="D34" s="6" t="s">
-        <v>18</v>
+        <v>94</v>
       </c>
     </row>
     <row r="35" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="B35" s="5" t="b">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="C35" s="6" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="D35" s="6" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
     </row>
     <row r="36" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
+        <v>17</v>
+      </c>
+      <c r="B36" s="5" t="b">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="C36" s="6" t="s">
         <v>19</v>
       </c>
-      <c r="B36" s="5" t="b">
-        <f t="shared" si="0"/>
-        <v>1</v>
-      </c>
-      <c r="C36" s="6" t="s">
-        <v>21</v>
-      </c>
       <c r="D36" s="6" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
     </row>
     <row r="37" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="B37" s="5" t="b">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="C37" s="6" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="D37" s="6" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
     </row>
     <row r="38" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="B38" s="5" t="b">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="C38" s="6" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="D38" s="6" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
     </row>
     <row r="39" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="B39" s="5" t="b">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="C39" s="6" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="D39" s="6" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
     </row>
     <row r="40" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="B40" s="5" t="b">
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
       <c r="C40" s="6" t="s">
-        <v>96</v>
+        <v>91</v>
       </c>
       <c r="D40" s="6" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
     </row>
     <row r="41" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="B41" s="5" t="b">
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
       <c r="C41" s="6" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="D41" s="6" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
     </row>
     <row r="42" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="B42" s="5" t="b">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="C42" s="6" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="D42" s="6" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
     </row>
     <row r="43" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="B43" s="5" t="b">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="C43" s="6" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="D43" s="6" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
     </row>
     <row r="44" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="B44" s="5" t="b">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="C44" s="6" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="D44" s="6" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
     </row>
     <row r="45" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="B45" s="5" t="b">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="C45" s="6" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="D45" s="6" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
     </row>
     <row r="46" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="B46" s="5" t="b">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="C46" s="6" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="D46" s="6" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
     </row>
     <row r="47" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="B47" s="5" t="b">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="C47" s="6" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="D47" s="6" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
     </row>
     <row r="48" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="B48" s="5" t="b">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="C48" s="6" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="D48" s="6" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
     </row>
     <row r="49" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
+        <v>33</v>
+      </c>
+      <c r="B49" s="5" t="b">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="C49" s="6" t="s">
         <v>35</v>
       </c>
-      <c r="B49" s="5" t="b">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="C49" s="6" t="s">
-        <v>37</v>
-      </c>
       <c r="D49" s="6" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
     </row>
     <row r="50" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="B50" s="5" t="b">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C50" s="6" t="s">
-        <v>38</v>
+        <v>93</v>
       </c>
       <c r="D50" s="6" t="s">
-        <v>38</v>
+        <v>92</v>
       </c>
     </row>
     <row r="51" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="B51" s="5" t="b">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="C51" s="6" t="s">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="D51" s="6" t="s">
-        <v>40</v>
+        <v>37</v>
       </c>
     </row>
     <row r="52" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="B52" s="5" t="b">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="C52" s="6" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="D52" s="6" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
     </row>
     <row r="53" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
+        <v>36</v>
+      </c>
+      <c r="B53" s="5" t="b">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="C53" s="6" t="s">
         <v>39</v>
       </c>
-      <c r="B53" s="5" t="b">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="C53" s="6" t="s">
-        <v>42</v>
-      </c>
       <c r="D53" s="6" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
     </row>
     <row r="54" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="B54" s="5" t="b">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="C54" s="6" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="D54" s="6" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
     </row>
     <row r="55" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="B55" s="5" t="b">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="C55" s="6" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="D55" s="6" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
     </row>
     <row r="56" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="B56" s="5" t="b">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="C56" s="6" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="D56" s="6" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
     </row>
     <row r="57" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="B57" s="5" t="b">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="C57" s="6" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="D57" s="6" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
     </row>
     <row r="58" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="B58" s="5" t="b">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="C58" s="6" t="s">
-        <v>48</v>
+        <v>96</v>
       </c>
       <c r="D58" s="6" t="s">
-        <v>48</v>
+        <v>96</v>
       </c>
     </row>
     <row r="59" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
+        <v>42</v>
+      </c>
+      <c r="B59" s="5" t="b">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="C59" s="6" t="s">
         <v>45</v>
       </c>
-      <c r="B59" s="5" t="b">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="C59" s="6" t="s">
-        <v>49</v>
-      </c>
       <c r="D59" s="6" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
     </row>
     <row r="60" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="B60" s="5" t="b">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="C60" s="6" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="D60" s="6" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
     </row>
     <row r="61" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="B61" s="5" t="b">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="C61" s="6" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="D61" s="6" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
     </row>
     <row r="62" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="B62" s="5" t="b">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="C62" s="6" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="D62" s="6" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
     </row>
     <row r="63" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="B63" s="5" t="b">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="C63" s="6" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="D63" s="6" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
     </row>
     <row r="64" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="B64" s="5" t="b">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="C64" s="6" t="s">
-        <v>55</v>
+        <v>51</v>
       </c>
       <c r="D64" s="6" t="s">
-        <v>55</v>
+        <v>51</v>
       </c>
     </row>
     <row r="65" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A65" t="s">
-        <v>56</v>
+        <v>52</v>
       </c>
       <c r="B65" s="5" t="b">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="C65" s="6" t="s">
-        <v>57</v>
+        <v>53</v>
       </c>
       <c r="D65" s="6" t="s">
-        <v>57</v>
+        <v>53</v>
       </c>
     </row>
     <row r="66" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A66" t="s">
-        <v>56</v>
+        <v>52</v>
       </c>
       <c r="B66" s="5" t="b">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="C66" s="6" t="s">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="D66" s="6" t="s">
-        <v>58</v>
+        <v>54</v>
       </c>
     </row>
     <row r="67" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A67" t="s">
-        <v>56</v>
+        <v>52</v>
       </c>
       <c r="B67" s="5" t="b">
         <f t="shared" ref="B67:B101" si="1">C67&lt;&gt;D67</f>
         <v>0</v>
       </c>
       <c r="C67" s="6" t="s">
-        <v>59</v>
+        <v>55</v>
       </c>
       <c r="D67" s="6" t="s">
-        <v>59</v>
+        <v>55</v>
       </c>
     </row>
     <row r="68" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A68" t="s">
+        <v>52</v>
+      </c>
+      <c r="B68" s="5" t="b">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="C68" s="6" t="s">
         <v>56</v>
       </c>
-      <c r="B68" s="5" t="b">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="C68" s="6" t="s">
-        <v>60</v>
-      </c>
       <c r="D68" s="6" t="s">
-        <v>60</v>
+        <v>56</v>
       </c>
     </row>
     <row r="69" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A69" t="s">
-        <v>56</v>
+        <v>52</v>
       </c>
       <c r="B69" s="5" t="b">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="C69" s="6" t="s">
-        <v>61</v>
+        <v>57</v>
       </c>
       <c r="D69" s="6" t="s">
-        <v>61</v>
+        <v>57</v>
       </c>
     </row>
     <row r="70" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A70" t="s">
-        <v>56</v>
+        <v>52</v>
       </c>
       <c r="B70" s="5" t="b">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="C70" s="6" t="s">
-        <v>62</v>
+        <v>58</v>
       </c>
       <c r="D70" s="6" t="s">
-        <v>62</v>
+        <v>58</v>
       </c>
     </row>
     <row r="71" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A71" t="s">
-        <v>63</v>
+        <v>59</v>
       </c>
       <c r="B71" s="5" t="b">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="C71" s="6" t="s">
-        <v>64</v>
+        <v>60</v>
       </c>
       <c r="D71" s="6" t="s">
-        <v>64</v>
+        <v>60</v>
       </c>
     </row>
     <row r="72" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A72" t="s">
-        <v>63</v>
+        <v>59</v>
       </c>
       <c r="B72" s="5" t="b">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="C72" s="6" t="s">
-        <v>65</v>
+        <v>61</v>
       </c>
       <c r="D72" s="6" t="s">
-        <v>65</v>
+        <v>61</v>
       </c>
     </row>
     <row r="73" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A73" t="s">
-        <v>63</v>
+        <v>59</v>
       </c>
       <c r="B73" s="5" t="b">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="C73" s="6" t="s">
-        <v>66</v>
+        <v>62</v>
       </c>
       <c r="D73" s="6" t="s">
-        <v>66</v>
+        <v>62</v>
       </c>
     </row>
     <row r="74" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A74" t="s">
+        <v>59</v>
+      </c>
+      <c r="B74" s="5" t="b">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="C74" s="6" t="s">
         <v>63</v>
       </c>
-      <c r="B74" s="5" t="b">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="C74" s="6" t="s">
-        <v>67</v>
-      </c>
       <c r="D74" s="6" t="s">
-        <v>67</v>
+        <v>63</v>
       </c>
     </row>
     <row r="75" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A75" t="s">
-        <v>63</v>
+        <v>59</v>
       </c>
       <c r="B75" s="5" t="b">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="C75" s="6" t="s">
-        <v>68</v>
+        <v>64</v>
       </c>
       <c r="D75" s="6" t="s">
-        <v>68</v>
+        <v>64</v>
       </c>
     </row>
     <row r="76" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A76" t="s">
-        <v>63</v>
+        <v>59</v>
       </c>
       <c r="B76" s="5" t="b">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="C76" s="6" t="s">
-        <v>69</v>
+        <v>65</v>
       </c>
       <c r="D76" s="6" t="s">
-        <v>69</v>
+        <v>65</v>
       </c>
     </row>
     <row r="77" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A77" t="s">
-        <v>63</v>
+        <v>59</v>
       </c>
       <c r="B77" s="5" t="b">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="C77" s="6" t="s">
-        <v>70</v>
+        <v>66</v>
       </c>
       <c r="D77" s="6" t="s">
-        <v>70</v>
+        <v>66</v>
       </c>
     </row>
     <row r="78" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A78" t="s">
-        <v>63</v>
+        <v>59</v>
       </c>
       <c r="B78" s="5" t="b">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="C78" s="6" t="s">
-        <v>71</v>
+        <v>67</v>
       </c>
       <c r="D78" s="6" t="s">
-        <v>71</v>
+        <v>67</v>
       </c>
     </row>
     <row r="79" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A79" t="s">
-        <v>63</v>
+        <v>59</v>
       </c>
       <c r="B79" s="5" t="b">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="C79" s="6" t="s">
-        <v>95</v>
+        <v>90</v>
       </c>
       <c r="D79" s="6" t="s">
-        <v>95</v>
+        <v>90</v>
       </c>
     </row>
     <row r="80" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A80" t="s">
-        <v>63</v>
+        <v>59</v>
       </c>
       <c r="B80" s="5" t="b">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="C80" s="6" t="s">
-        <v>72</v>
+        <v>68</v>
       </c>
       <c r="D80" s="6" t="s">
-        <v>72</v>
+        <v>68</v>
       </c>
     </row>
     <row r="81" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A81" t="s">
-        <v>63</v>
+        <v>59</v>
       </c>
       <c r="B81" s="5" t="b">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="C81" s="6" t="s">
-        <v>73</v>
+        <v>69</v>
       </c>
       <c r="D81" s="6" t="s">
-        <v>73</v>
+        <v>69</v>
       </c>
     </row>
     <row r="82" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A82" t="s">
-        <v>63</v>
+        <v>59</v>
       </c>
       <c r="B82" s="5" t="b">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="C82" s="6" t="s">
-        <v>74</v>
+        <v>70</v>
       </c>
       <c r="D82" s="6" t="s">
-        <v>74</v>
+        <v>70</v>
       </c>
     </row>
     <row r="83" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A83" t="s">
-        <v>63</v>
+        <v>59</v>
       </c>
       <c r="B83" s="5" t="b">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="C83" s="6" t="s">
-        <v>75</v>
+        <v>71</v>
       </c>
       <c r="D83" s="6" t="s">
-        <v>75</v>
+        <v>71</v>
       </c>
     </row>
     <row r="84" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A84" t="s">
-        <v>63</v>
+        <v>59</v>
       </c>
       <c r="B84" s="5" t="b">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="C84" s="6" t="s">
-        <v>76</v>
+        <v>72</v>
       </c>
       <c r="D84" s="6" t="s">
-        <v>76</v>
+        <v>72</v>
       </c>
     </row>
     <row r="85" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A85" t="s">
-        <v>63</v>
+        <v>59</v>
       </c>
       <c r="B85" s="5" t="b">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="C85" s="6" t="s">
-        <v>77</v>
+        <v>73</v>
       </c>
       <c r="D85" s="6" t="s">
-        <v>77</v>
+        <v>73</v>
       </c>
     </row>
     <row r="86" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A86" t="s">
-        <v>63</v>
+        <v>59</v>
       </c>
       <c r="B86" s="5" t="b">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="C86" s="6" t="s">
-        <v>78</v>
+        <v>74</v>
       </c>
       <c r="D86" s="6" t="s">
-        <v>78</v>
+        <v>74</v>
       </c>
     </row>
     <row r="87" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A87" t="s">
-        <v>63</v>
+        <v>59</v>
       </c>
       <c r="B87" s="5" t="b">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="C87" s="6" t="s">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="D87" s="6" t="s">
-        <v>79</v>
+        <v>75</v>
       </c>
     </row>
     <row r="88" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A88" t="s">
-        <v>63</v>
+        <v>59</v>
       </c>
       <c r="B88" s="5" t="b">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="C88" s="6" t="s">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="D88" s="6" t="s">
-        <v>80</v>
+        <v>76</v>
       </c>
     </row>
     <row r="89" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A89" t="s">
-        <v>63</v>
+        <v>59</v>
       </c>
       <c r="B89" s="5" t="b">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="C89" s="6" t="s">
-        <v>81</v>
+        <v>77</v>
       </c>
       <c r="D89" s="6" t="s">
-        <v>81</v>
+        <v>77</v>
       </c>
     </row>
     <row r="90" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A90" t="s">
-        <v>63</v>
+        <v>59</v>
       </c>
       <c r="B90" s="5" t="b">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="C90" s="6" t="s">
-        <v>82</v>
+        <v>78</v>
       </c>
       <c r="D90" s="6" t="s">
-        <v>82</v>
+        <v>78</v>
       </c>
     </row>
     <row r="91" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A91" t="s">
-        <v>63</v>
+        <v>59</v>
       </c>
       <c r="B91" s="5" t="b">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="C91" s="6" t="s">
-        <v>83</v>
+        <v>79</v>
       </c>
       <c r="D91" s="6" t="s">
-        <v>83</v>
+        <v>79</v>
       </c>
     </row>
     <row r="92" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A92" t="s">
-        <v>84</v>
+        <v>80</v>
       </c>
       <c r="B92" s="5" t="b">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="C92" s="6" t="s">
-        <v>85</v>
+        <v>81</v>
       </c>
       <c r="D92" s="6" t="s">
-        <v>85</v>
+        <v>81</v>
       </c>
     </row>
     <row r="93" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A93" t="s">
-        <v>84</v>
+        <v>80</v>
       </c>
       <c r="B93" s="5" t="b">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="C93" s="6" t="s">
-        <v>86</v>
+        <v>82</v>
       </c>
       <c r="D93" s="6" t="s">
-        <v>86</v>
+        <v>82</v>
       </c>
     </row>
     <row r="94" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A94" t="s">
-        <v>84</v>
+        <v>80</v>
       </c>
       <c r="B94" s="5" t="b">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="C94" s="6" t="s">
-        <v>87</v>
+        <v>83</v>
       </c>
       <c r="D94" s="6" t="s">
-        <v>87</v>
+        <v>83</v>
       </c>
     </row>
     <row r="95" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A95" t="s">
+        <v>80</v>
+      </c>
+      <c r="B95" s="5" t="b">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="C95" s="6" t="s">
         <v>84</v>
       </c>
-      <c r="B95" s="5" t="b">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="C95" s="6" t="s">
-        <v>88</v>
-      </c>
       <c r="D95" s="6" t="s">
-        <v>88</v>
+        <v>84</v>
       </c>
     </row>
     <row r="96" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A96" t="s">
-        <v>84</v>
+        <v>80</v>
       </c>
       <c r="B96" s="5" t="b">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="C96" s="6" t="s">
-        <v>89</v>
+        <v>85</v>
       </c>
       <c r="D96" s="6" t="s">
-        <v>89</v>
+        <v>85</v>
       </c>
     </row>
     <row r="97" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A97" t="s">
-        <v>84</v>
+        <v>80</v>
       </c>
       <c r="B97" s="5" t="b">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="C97" s="6" t="s">
-        <v>90</v>
+        <v>86</v>
       </c>
       <c r="D97" s="6" t="s">
-        <v>90</v>
+        <v>86</v>
       </c>
     </row>
     <row r="98" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A98" t="s">
-        <v>84</v>
+        <v>80</v>
       </c>
       <c r="B98" s="5" t="b">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="C98" s="6" t="s">
-        <v>91</v>
+        <v>87</v>
       </c>
       <c r="D98" s="6" t="s">
-        <v>91</v>
+        <v>87</v>
       </c>
     </row>
     <row r="99" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A99" t="s">
-        <v>84</v>
+        <v>80</v>
       </c>
       <c r="B99" s="5" t="b">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="C99" s="6" t="s">
-        <v>92</v>
+        <v>97</v>
       </c>
       <c r="D99" s="6" t="s">
-        <v>92</v>
+        <v>97</v>
       </c>
     </row>
     <row r="100" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A100" t="s">
-        <v>84</v>
+        <v>80</v>
       </c>
       <c r="B100" s="5" t="b">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="C100" s="6" t="s">
-        <v>93</v>
+        <v>88</v>
       </c>
       <c r="D100" s="6" t="s">
-        <v>93</v>
+        <v>88</v>
       </c>
     </row>
     <row r="101" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A101" t="s">
-        <v>84</v>
+        <v>80</v>
       </c>
       <c r="B101" s="5" t="b">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="C101" s="6" t="s">
-        <v>94</v>
+        <v>89</v>
       </c>
       <c r="D101" s="6" t="s">
-        <v>94</v>
+        <v>89</v>
       </c>
     </row>
   </sheetData>

--- a/Decks/Jhoira.xlsx
+++ b/Decks/Jhoira.xlsx
@@ -5,12 +5,12 @@
   <workbookPr codeName="EstaPastaDeTrabalho" defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Marcelo Scalvi\Dropbox\Jogos\TheMagicCollection\Decks\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Usuario\Dropbox\Jogos\TheMagicCollection\Decks\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BE2D9EF8-F6A7-44F0-91E2-B8CCECE6389C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EC759B96-3435-43D2-AD79-3424DA384982}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{3A3EB0A0-3066-449C-BD01-AEAF92EDBA4C}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{3A3EB0A0-3066-449C-BD01-AEAF92EDBA4C}"/>
   </bookViews>
   <sheets>
     <sheet name="Jhoira" sheetId="1" r:id="rId1"/>
@@ -329,7 +329,7 @@
     <t>Evacuation</t>
   </si>
   <si>
-    <t>Antecipate</t>
+    <t>Anticipate</t>
   </si>
 </sst>
 </file>

--- a/Decks/Jhoira.xlsx
+++ b/Decks/Jhoira.xlsx
@@ -5,12 +5,12 @@
   <workbookPr codeName="EstaPastaDeTrabalho" defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Usuario\Dropbox\Jogos\TheMagicCollection\Decks\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Marcelo Scalvi\Dropbox\Jogos\TheMagicCollection\Decks\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EC759B96-3435-43D2-AD79-3424DA384982}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0CEE187B-8513-483D-A82E-3338ED9F4C55}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{3A3EB0A0-3066-449C-BD01-AEAF92EDBA4C}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{3A3EB0A0-3066-449C-BD01-AEAF92EDBA4C}"/>
   </bookViews>
   <sheets>
     <sheet name="Jhoira" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="306" uniqueCount="98">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="306" uniqueCount="99">
   <si>
     <t>Função</t>
   </si>
@@ -330,6 +330,9 @@
   </si>
   <si>
     <t>Anticipate</t>
+  </si>
+  <si>
+    <t>Stormcarved Coast</t>
   </si>
 </sst>
 </file>
@@ -907,10 +910,10 @@
         <v>0</v>
       </c>
       <c r="C11" s="6" t="s">
-        <v>95</v>
+        <v>98</v>
       </c>
       <c r="D11" s="6" t="s">
-        <v>95</v>
+        <v>98</v>
       </c>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.25">
@@ -1087,10 +1090,10 @@
         <v>0</v>
       </c>
       <c r="C23" s="6" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="D23" s="6" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
     </row>
     <row r="24" spans="1:4" x14ac:dyDescent="0.25">

--- a/Decks/Jhoira.xlsx
+++ b/Decks/Jhoira.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
   <workbookPr codeName="EstaPastaDeTrabalho" defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Marcelo Scalvi\Dropbox\Jogos\TheMagicCollection\Decks\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0CEE187B-8513-483D-A82E-3338ED9F4C55}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A7A67D0F-8863-4CDC-B94E-3758A1A6459E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{3A3EB0A0-3066-449C-BD01-AEAF92EDBA4C}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="306" uniqueCount="99">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="306" uniqueCount="98">
   <si>
     <t>Função</t>
   </si>
@@ -95,9 +95,6 @@
     <t>Emrakul, the Promised End</t>
   </si>
   <si>
-    <t>Consecrated Sphinx</t>
-  </si>
-  <si>
     <t>Emrakul, the World Anew</t>
   </si>
   <si>
@@ -299,9 +296,6 @@
     <t>Academy Loremaster</t>
   </si>
   <si>
-    <t>Serum Visions</t>
-  </si>
-  <si>
     <t>Impulse</t>
   </si>
   <si>
@@ -317,9 +311,6 @@
     <t>Improvisation Capstone</t>
   </si>
   <si>
-    <t>Mind's Dilation</t>
-  </si>
-  <si>
     <t>Mountain</t>
   </si>
   <si>
@@ -333,6 +324,12 @@
   </si>
   <si>
     <t>Stormcarved Coast</t>
+  </si>
+  <si>
+    <t>Shivan Reef</t>
+  </si>
+  <si>
+    <t>?</t>
   </si>
 </sst>
 </file>
@@ -865,7 +862,7 @@
         <v>1</v>
       </c>
       <c r="C8" s="6" t="s">
-        <v>95</v>
+        <v>92</v>
       </c>
       <c r="D8" s="6" t="s">
         <v>14</v>
@@ -880,7 +877,7 @@
         <v>1</v>
       </c>
       <c r="C9" s="6" t="s">
-        <v>95</v>
+        <v>92</v>
       </c>
       <c r="D9" s="6" t="s">
         <v>15</v>
@@ -895,7 +892,7 @@
         <v>1</v>
       </c>
       <c r="C10" s="6" t="s">
-        <v>95</v>
+        <v>92</v>
       </c>
       <c r="D10" s="6" t="s">
         <v>16</v>
@@ -910,10 +907,10 @@
         <v>0</v>
       </c>
       <c r="C11" s="6" t="s">
-        <v>98</v>
+        <v>95</v>
       </c>
       <c r="D11" s="6" t="s">
-        <v>98</v>
+        <v>95</v>
       </c>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.25">
@@ -925,10 +922,10 @@
         <v>0</v>
       </c>
       <c r="C12" s="6" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="D12" s="6" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.25">
@@ -940,10 +937,10 @@
         <v>0</v>
       </c>
       <c r="C13" s="6" t="s">
-        <v>95</v>
+        <v>92</v>
       </c>
       <c r="D13" s="6" t="s">
-        <v>95</v>
+        <v>92</v>
       </c>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.25">
@@ -955,10 +952,10 @@
         <v>0</v>
       </c>
       <c r="C14" s="6" t="s">
-        <v>95</v>
+        <v>92</v>
       </c>
       <c r="D14" s="6" t="s">
-        <v>95</v>
+        <v>92</v>
       </c>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.25">
@@ -970,10 +967,10 @@
         <v>0</v>
       </c>
       <c r="C15" s="6" t="s">
-        <v>95</v>
+        <v>92</v>
       </c>
       <c r="D15" s="6" t="s">
-        <v>95</v>
+        <v>92</v>
       </c>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.25">
@@ -985,10 +982,10 @@
         <v>0</v>
       </c>
       <c r="C16" s="6" t="s">
-        <v>95</v>
+        <v>92</v>
       </c>
       <c r="D16" s="6" t="s">
-        <v>95</v>
+        <v>92</v>
       </c>
     </row>
     <row r="17" spans="1:4" x14ac:dyDescent="0.25">
@@ -1000,10 +997,10 @@
         <v>0</v>
       </c>
       <c r="C17" s="6" t="s">
-        <v>95</v>
+        <v>92</v>
       </c>
       <c r="D17" s="6" t="s">
-        <v>95</v>
+        <v>92</v>
       </c>
     </row>
     <row r="18" spans="1:4" x14ac:dyDescent="0.25">
@@ -1015,10 +1012,10 @@
         <v>0</v>
       </c>
       <c r="C18" s="6" t="s">
-        <v>95</v>
+        <v>92</v>
       </c>
       <c r="D18" s="6" t="s">
-        <v>95</v>
+        <v>92</v>
       </c>
     </row>
     <row r="19" spans="1:4" x14ac:dyDescent="0.25">
@@ -1030,10 +1027,10 @@
         <v>0</v>
       </c>
       <c r="C19" s="6" t="s">
-        <v>95</v>
+        <v>92</v>
       </c>
       <c r="D19" s="6" t="s">
-        <v>95</v>
+        <v>92</v>
       </c>
     </row>
     <row r="20" spans="1:4" x14ac:dyDescent="0.25">
@@ -1045,10 +1042,10 @@
         <v>0</v>
       </c>
       <c r="C20" s="6" t="s">
-        <v>95</v>
+        <v>92</v>
       </c>
       <c r="D20" s="6" t="s">
-        <v>95</v>
+        <v>92</v>
       </c>
     </row>
     <row r="21" spans="1:4" x14ac:dyDescent="0.25">
@@ -1060,10 +1057,10 @@
         <v>0</v>
       </c>
       <c r="C21" s="6" t="s">
-        <v>95</v>
+        <v>92</v>
       </c>
       <c r="D21" s="6" t="s">
-        <v>95</v>
+        <v>92</v>
       </c>
     </row>
     <row r="22" spans="1:4" x14ac:dyDescent="0.25">
@@ -1075,10 +1072,10 @@
         <v>0</v>
       </c>
       <c r="C22" s="6" t="s">
-        <v>95</v>
+        <v>92</v>
       </c>
       <c r="D22" s="6" t="s">
-        <v>95</v>
+        <v>92</v>
       </c>
     </row>
     <row r="23" spans="1:4" x14ac:dyDescent="0.25">
@@ -1090,10 +1087,10 @@
         <v>0</v>
       </c>
       <c r="C23" s="6" t="s">
-        <v>95</v>
+        <v>92</v>
       </c>
       <c r="D23" s="6" t="s">
-        <v>95</v>
+        <v>92</v>
       </c>
     </row>
     <row r="24" spans="1:4" x14ac:dyDescent="0.25">
@@ -1105,10 +1102,10 @@
         <v>0</v>
       </c>
       <c r="C24" s="6" t="s">
-        <v>94</v>
+        <v>91</v>
       </c>
       <c r="D24" s="6" t="s">
-        <v>94</v>
+        <v>91</v>
       </c>
     </row>
     <row r="25" spans="1:4" x14ac:dyDescent="0.25">
@@ -1120,10 +1117,10 @@
         <v>0</v>
       </c>
       <c r="C25" s="6" t="s">
-        <v>94</v>
+        <v>91</v>
       </c>
       <c r="D25" s="6" t="s">
-        <v>94</v>
+        <v>91</v>
       </c>
     </row>
     <row r="26" spans="1:4" x14ac:dyDescent="0.25">
@@ -1135,10 +1132,10 @@
         <v>0</v>
       </c>
       <c r="C26" s="6" t="s">
-        <v>94</v>
+        <v>91</v>
       </c>
       <c r="D26" s="6" t="s">
-        <v>94</v>
+        <v>91</v>
       </c>
     </row>
     <row r="27" spans="1:4" x14ac:dyDescent="0.25">
@@ -1150,10 +1147,10 @@
         <v>0</v>
       </c>
       <c r="C27" s="6" t="s">
-        <v>94</v>
+        <v>91</v>
       </c>
       <c r="D27" s="6" t="s">
-        <v>94</v>
+        <v>91</v>
       </c>
     </row>
     <row r="28" spans="1:4" x14ac:dyDescent="0.25">
@@ -1165,10 +1162,10 @@
         <v>0</v>
       </c>
       <c r="C28" s="6" t="s">
-        <v>94</v>
+        <v>91</v>
       </c>
       <c r="D28" s="6" t="s">
-        <v>94</v>
+        <v>91</v>
       </c>
     </row>
     <row r="29" spans="1:4" x14ac:dyDescent="0.25">
@@ -1180,10 +1177,10 @@
         <v>0</v>
       </c>
       <c r="C29" s="6" t="s">
-        <v>94</v>
+        <v>91</v>
       </c>
       <c r="D29" s="6" t="s">
-        <v>94</v>
+        <v>91</v>
       </c>
     </row>
     <row r="30" spans="1:4" x14ac:dyDescent="0.25">
@@ -1195,10 +1192,10 @@
         <v>0</v>
       </c>
       <c r="C30" s="6" t="s">
-        <v>94</v>
+        <v>91</v>
       </c>
       <c r="D30" s="6" t="s">
-        <v>94</v>
+        <v>91</v>
       </c>
     </row>
     <row r="31" spans="1:4" x14ac:dyDescent="0.25">
@@ -1210,10 +1207,10 @@
         <v>0</v>
       </c>
       <c r="C31" s="6" t="s">
-        <v>94</v>
+        <v>91</v>
       </c>
       <c r="D31" s="6" t="s">
-        <v>94</v>
+        <v>91</v>
       </c>
     </row>
     <row r="32" spans="1:4" x14ac:dyDescent="0.25">
@@ -1225,10 +1222,10 @@
         <v>0</v>
       </c>
       <c r="C32" s="6" t="s">
-        <v>94</v>
+        <v>91</v>
       </c>
       <c r="D32" s="6" t="s">
-        <v>94</v>
+        <v>91</v>
       </c>
     </row>
     <row r="33" spans="1:4" x14ac:dyDescent="0.25">
@@ -1240,10 +1237,10 @@
         <v>0</v>
       </c>
       <c r="C33" s="6" t="s">
-        <v>94</v>
+        <v>91</v>
       </c>
       <c r="D33" s="6" t="s">
-        <v>94</v>
+        <v>91</v>
       </c>
     </row>
     <row r="34" spans="1:4" x14ac:dyDescent="0.25">
@@ -1255,10 +1252,10 @@
         <v>0</v>
       </c>
       <c r="C34" s="6" t="s">
-        <v>94</v>
+        <v>91</v>
       </c>
       <c r="D34" s="6" t="s">
-        <v>94</v>
+        <v>91</v>
       </c>
     </row>
     <row r="35" spans="1:4" x14ac:dyDescent="0.25">
@@ -1282,13 +1279,13 @@
       </c>
       <c r="B36" s="5" t="b">
         <f t="shared" si="0"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C36" s="6" t="s">
         <v>19</v>
       </c>
       <c r="D36" s="6" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="37" spans="1:4" x14ac:dyDescent="0.25">
@@ -1300,10 +1297,10 @@
         <v>0</v>
       </c>
       <c r="C37" s="6" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="D37" s="6" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
     <row r="38" spans="1:4" x14ac:dyDescent="0.25">
@@ -1315,10 +1312,10 @@
         <v>0</v>
       </c>
       <c r="C38" s="6" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D38" s="6" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="39" spans="1:4" x14ac:dyDescent="0.25">
@@ -1330,10 +1327,10 @@
         <v>0</v>
       </c>
       <c r="C39" s="6" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="D39" s="6" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="40" spans="1:4" x14ac:dyDescent="0.25">
@@ -1345,10 +1342,10 @@
         <v>1</v>
       </c>
       <c r="C40" s="6" t="s">
-        <v>91</v>
+        <v>97</v>
       </c>
       <c r="D40" s="6" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="41" spans="1:4" x14ac:dyDescent="0.25">
@@ -1360,10 +1357,10 @@
         <v>1</v>
       </c>
       <c r="C41" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="D41" s="6" t="s">
         <v>25</v>
-      </c>
-      <c r="D41" s="6" t="s">
-        <v>26</v>
       </c>
     </row>
     <row r="42" spans="1:4" x14ac:dyDescent="0.25">
@@ -1375,10 +1372,10 @@
         <v>0</v>
       </c>
       <c r="C42" s="6" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="D42" s="6" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
     </row>
     <row r="43" spans="1:4" x14ac:dyDescent="0.25">
@@ -1390,10 +1387,10 @@
         <v>0</v>
       </c>
       <c r="C43" s="6" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="D43" s="6" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="44" spans="1:4" x14ac:dyDescent="0.25">
@@ -1405,10 +1402,10 @@
         <v>0</v>
       </c>
       <c r="C44" s="6" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="D44" s="6" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
     </row>
     <row r="45" spans="1:4" x14ac:dyDescent="0.25">
@@ -1420,10 +1417,10 @@
         <v>0</v>
       </c>
       <c r="C45" s="6" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D45" s="6" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
     </row>
     <row r="46" spans="1:4" x14ac:dyDescent="0.25">
@@ -1435,10 +1432,10 @@
         <v>0</v>
       </c>
       <c r="C46" s="6" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="D46" s="6" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
     </row>
     <row r="47" spans="1:4" x14ac:dyDescent="0.25">
@@ -1450,820 +1447,820 @@
         <v>0</v>
       </c>
       <c r="C47" s="6" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="D47" s="6" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="48" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
+        <v>32</v>
+      </c>
+      <c r="B48" s="5" t="b">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="C48" s="6" t="s">
         <v>33</v>
       </c>
-      <c r="B48" s="5" t="b">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="C48" s="6" t="s">
-        <v>34</v>
-      </c>
       <c r="D48" s="6" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
     </row>
     <row r="49" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B49" s="5" t="b">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="C49" s="6" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="D49" s="6" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
     </row>
     <row r="50" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B50" s="5" t="b">
         <f t="shared" si="0"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C50" s="6" t="s">
-        <v>93</v>
+        <v>90</v>
       </c>
       <c r="D50" s="6" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
     </row>
     <row r="51" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
+        <v>35</v>
+      </c>
+      <c r="B51" s="5" t="b">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="C51" s="6" t="s">
         <v>36</v>
       </c>
-      <c r="B51" s="5" t="b">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="C51" s="6" t="s">
-        <v>37</v>
-      </c>
       <c r="D51" s="6" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
     </row>
     <row r="52" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="B52" s="5" t="b">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="C52" s="6" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="D52" s="6" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
     </row>
     <row r="53" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="B53" s="5" t="b">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="C53" s="6" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="D53" s="6" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
     <row r="54" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="B54" s="5" t="b">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="C54" s="6" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="D54" s="6" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
     </row>
     <row r="55" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="B55" s="5" t="b">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="C55" s="6" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="D55" s="6" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
     </row>
     <row r="56" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
+        <v>41</v>
+      </c>
+      <c r="B56" s="5" t="b">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="C56" s="6" t="s">
         <v>42</v>
       </c>
-      <c r="B56" s="5" t="b">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="C56" s="6" t="s">
-        <v>43</v>
-      </c>
       <c r="D56" s="6" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
     </row>
     <row r="57" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B57" s="5" t="b">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="C57" s="6" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="D57" s="6" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
     </row>
     <row r="58" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B58" s="5" t="b">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="C58" s="6" t="s">
-        <v>96</v>
+        <v>93</v>
       </c>
       <c r="D58" s="6" t="s">
-        <v>96</v>
+        <v>93</v>
       </c>
     </row>
     <row r="59" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B59" s="5" t="b">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="C59" s="6" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="D59" s="6" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
     </row>
     <row r="60" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B60" s="5" t="b">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="C60" s="6" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="D60" s="6" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
     </row>
     <row r="61" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B61" s="5" t="b">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="C61" s="6" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D61" s="6" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
     </row>
     <row r="62" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B62" s="5" t="b">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="C62" s="6" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="D62" s="6" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
     </row>
     <row r="63" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
+        <v>48</v>
+      </c>
+      <c r="B63" s="5" t="b">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="C63" s="6" t="s">
         <v>49</v>
       </c>
-      <c r="B63" s="5" t="b">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="C63" s="6" t="s">
-        <v>50</v>
-      </c>
       <c r="D63" s="6" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
     </row>
     <row r="64" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="B64" s="5" t="b">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="C64" s="6" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="D64" s="6" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
     </row>
     <row r="65" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A65" t="s">
+        <v>51</v>
+      </c>
+      <c r="B65" s="5" t="b">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="C65" s="6" t="s">
         <v>52</v>
       </c>
-      <c r="B65" s="5" t="b">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="C65" s="6" t="s">
-        <v>53</v>
-      </c>
       <c r="D65" s="6" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
     </row>
     <row r="66" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A66" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="B66" s="5" t="b">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="C66" s="6" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="D66" s="6" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
     </row>
     <row r="67" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A67" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="B67" s="5" t="b">
         <f t="shared" ref="B67:B101" si="1">C67&lt;&gt;D67</f>
         <v>0</v>
       </c>
       <c r="C67" s="6" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="D67" s="6" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
     </row>
     <row r="68" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A68" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="B68" s="5" t="b">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="C68" s="6" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="D68" s="6" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
     </row>
     <row r="69" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A69" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="B69" s="5" t="b">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="C69" s="6" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="D69" s="6" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
     </row>
     <row r="70" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A70" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="B70" s="5" t="b">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="C70" s="6" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="D70" s="6" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
     </row>
     <row r="71" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A71" t="s">
+        <v>58</v>
+      </c>
+      <c r="B71" s="5" t="b">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="C71" s="6" t="s">
         <v>59</v>
       </c>
-      <c r="B71" s="5" t="b">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="C71" s="6" t="s">
-        <v>60</v>
-      </c>
       <c r="D71" s="6" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
     </row>
     <row r="72" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A72" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="B72" s="5" t="b">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="C72" s="6" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="D72" s="6" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
     </row>
     <row r="73" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A73" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="B73" s="5" t="b">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="C73" s="6" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="D73" s="6" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
     </row>
     <row r="74" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A74" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="B74" s="5" t="b">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="C74" s="6" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="D74" s="6" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
     </row>
     <row r="75" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A75" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="B75" s="5" t="b">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="C75" s="6" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="D75" s="6" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
     </row>
     <row r="76" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A76" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="B76" s="5" t="b">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="C76" s="6" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="D76" s="6" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
     </row>
     <row r="77" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A77" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="B77" s="5" t="b">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="C77" s="6" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="D77" s="6" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
     </row>
     <row r="78" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A78" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="B78" s="5" t="b">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="C78" s="6" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="D78" s="6" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
     </row>
     <row r="79" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A79" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="B79" s="5" t="b">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="C79" s="6" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="D79" s="6" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
     </row>
     <row r="80" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A80" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="B80" s="5" t="b">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="C80" s="6" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="D80" s="6" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
     </row>
     <row r="81" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A81" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="B81" s="5" t="b">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="C81" s="6" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="D81" s="6" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
     </row>
     <row r="82" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A82" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="B82" s="5" t="b">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="C82" s="6" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="D82" s="6" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
     </row>
     <row r="83" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A83" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="B83" s="5" t="b">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="C83" s="6" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="D83" s="6" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
     </row>
     <row r="84" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A84" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="B84" s="5" t="b">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="C84" s="6" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="D84" s="6" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
     </row>
     <row r="85" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A85" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="B85" s="5" t="b">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="C85" s="6" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="D85" s="6" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
     </row>
     <row r="86" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A86" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="B86" s="5" t="b">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="C86" s="6" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="D86" s="6" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
     </row>
     <row r="87" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A87" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="B87" s="5" t="b">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="C87" s="6" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="D87" s="6" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
     </row>
     <row r="88" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A88" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="B88" s="5" t="b">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="C88" s="6" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="D88" s="6" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
     </row>
     <row r="89" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A89" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="B89" s="5" t="b">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="C89" s="6" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="D89" s="6" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
     </row>
     <row r="90" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A90" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="B90" s="5" t="b">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="C90" s="6" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="D90" s="6" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
     </row>
     <row r="91" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A91" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="B91" s="5" t="b">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="C91" s="6" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="D91" s="6" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
     </row>
     <row r="92" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A92" t="s">
+        <v>79</v>
+      </c>
+      <c r="B92" s="5" t="b">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="C92" s="6" t="s">
         <v>80</v>
       </c>
-      <c r="B92" s="5" t="b">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="C92" s="6" t="s">
-        <v>81</v>
-      </c>
       <c r="D92" s="6" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
     </row>
     <row r="93" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A93" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="B93" s="5" t="b">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="C93" s="6" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="D93" s="6" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
     </row>
     <row r="94" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A94" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="B94" s="5" t="b">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="C94" s="6" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="D94" s="6" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
     </row>
     <row r="95" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A95" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="B95" s="5" t="b">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="C95" s="6" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="D95" s="6" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
     </row>
     <row r="96" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A96" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="B96" s="5" t="b">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="C96" s="6" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="D96" s="6" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
     </row>
     <row r="97" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A97" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="B97" s="5" t="b">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="C97" s="6" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="D97" s="6" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
     </row>
     <row r="98" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A98" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="B98" s="5" t="b">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="C98" s="6" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="D98" s="6" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
     </row>
     <row r="99" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A99" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="B99" s="5" t="b">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="C99" s="6" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="D99" s="6" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
     </row>
     <row r="100" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A100" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="B100" s="5" t="b">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="C100" s="6" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="D100" s="6" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
     </row>
     <row r="101" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A101" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="B101" s="5" t="b">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="C101" s="6" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="D101" s="6" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
     </row>
   </sheetData>

--- a/Decks/Jhoira.xlsx
+++ b/Decks/Jhoira.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
   <workbookPr codeName="EstaPastaDeTrabalho" defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Marcelo Scalvi\Dropbox\Jogos\TheMagicCollection\Decks\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A7A67D0F-8863-4CDC-B94E-3758A1A6459E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6406CE6C-8A24-4885-A425-BA0D749A1654}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{3A3EB0A0-3066-449C-BD01-AEAF92EDBA4C}"/>
   </bookViews>
@@ -329,7 +329,7 @@
     <t>Shivan Reef</t>
   </si>
   <si>
-    <t>?</t>
+    <t>Proteção</t>
   </si>
 </sst>
 </file>
@@ -874,10 +874,10 @@
       </c>
       <c r="B9" s="5" t="b">
         <f t="shared" si="0"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C9" s="6" t="s">
-        <v>92</v>
+        <v>15</v>
       </c>
       <c r="D9" s="6" t="s">
         <v>15</v>
@@ -1324,10 +1324,10 @@
       </c>
       <c r="B39" s="5" t="b">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C39" s="6" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="D39" s="6" t="s">
         <v>22</v>
@@ -1339,10 +1339,10 @@
       </c>
       <c r="B40" s="5" t="b">
         <f t="shared" si="0"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C40" s="6" t="s">
-        <v>97</v>
+        <v>23</v>
       </c>
       <c r="D40" s="6" t="s">
         <v>23</v>
@@ -1354,10 +1354,10 @@
       </c>
       <c r="B41" s="5" t="b">
         <f t="shared" si="0"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C41" s="6" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="D41" s="6" t="s">
         <v>25</v>
@@ -2085,7 +2085,7 @@
     </row>
     <row r="90" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A90" t="s">
-        <v>58</v>
+        <v>97</v>
       </c>
       <c r="B90" s="5" t="b">
         <f t="shared" si="1"/>
@@ -2100,7 +2100,7 @@
     </row>
     <row r="91" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A91" t="s">
-        <v>58</v>
+        <v>97</v>
       </c>
       <c r="B91" s="5" t="b">
         <f t="shared" si="1"/>
